--- a/InputFiles/CTDC/TC02_CTDC_AnatomCollecSite-Neck.xlsx
+++ b/InputFiles/CTDC/TC02_CTDC_AnatomCollecSite-Neck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\CTDC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/CTDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9363B242-6DE7-4A3C-B373-C06480DB3927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6DAE14-956B-7040-8BDB-014FFC7A8F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="23260" windowHeight="12460" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -148,74 +148,6 @@
         ON prt.participant_id = fil."participant.participant_id"
 WHERE 
     std.study_id = 'NCT04314401' AND bio.anatomical_collection_site = 'Neck'
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    fil.data_file_name AS "File Name",
-    fil.data_file_format AS "Format",
-    fil.data_file_type AS "File Type",
-CASE     
-    WHEN fil.data_file_size &gt;= 1024 * 1024 * 1024 THEN 
-        CASE 
-            WHEN ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 2) = CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) 
-            THEN CAST(CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' GB'
-            ELSE ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 2) || ' GB'
-        END
-    WHEN fil.data_file_size &gt;= 1024 * 1024 THEN 
-        CASE 
-            WHEN ROUND(fil.data_file_size / (1024.0 * 1024.0), 2) = CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0), 0) AS INT) 
-            THEN CAST(CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' MB'
-            ELSE ROUND(fil.data_file_size / (1024.0 * 1024.0), 2) || ' MB'
-        END
-    WHEN fil.data_file_size &gt;= 1024 THEN 
-        CASE 
-            WHEN ROUND(fil.data_file_size / 1024.0, 2) = CAST(ROUND(fil.data_file_size / 1024.0, 0) AS INT) 
-            THEN CAST(CAST(ROUND(fil.data_file_size / 1024.0, 0) AS INT) AS TEXT) || ' KB'
-            ELSE ROUND(fil.data_file_size / 1024.0, 2) || ' KB'
-        END
-    ELSE 
-        CASE 
-            WHEN ROUND(fil.data_file_size, 2) = CAST(ROUND(fil.data_file_size, 0) AS INT) 
-            THEN CAST(CAST(ROUND(fil.data_file_size, 0) AS INT) AS TEXT) || ' Bytes'
-            ELSE ROUND(fil.data_file_size, 2) || ' Bytes'
-        END
-    END AS "Size",
-    fil.data_file_description AS "Description",
-    fil."specimen.specimen_record_id" AS "Specimen Record ID",
-    prt.participant_id AS "Participant ID",
-    dgn.ctep_disease_term AS "Diagnosis"
-FROM 
-    df_study std
-LEFT JOIN 
-    df_participant prt 
-        ON std.study_short_name = prt."study.study_short_name"
-LEFT JOIN 
-    df_diagnosis dgn 
-        ON prt.participant_id = dgn."participant.participant_id"
-LEFT JOIN 
-    df_demographic demo 
-        ON prt.participant_id = demo."participant.participant_id"
-LEFT JOIN 
-    df_exposure exp 
-        ON prt.participant_id = exp."participant.participant_id"
-LEFT JOIN 
-    df_targeted_therapy tgt 
-        ON prt.participant_id = tgt."participant.participant_id"
-LEFT JOIN 
-    df_non_targeted_therapy ntt 
-        ON prt.participant_id = ntt."participant.participant_id"
-LEFT JOIN 
-    df_participant_status pst 
-        ON prt.participant_id = pst."participant.participant_id"
-LEFT JOIN 
-    df_biospecimen bio 
-        ON prt.participant_id = bio."participant.participant_id"
-LEFT JOIN 
-    df_file fil 
-        ON bio.specimen_record_id = fil."specimen.specimen_record_id"
-WHERE 
-    std.study_id = 'NCT04314401' AND bio.anatomical_collection_site = 'Neck' AND fil.data_file_name IS NOT NULL
 LIMIT 100;</t>
   </si>
   <si>
@@ -267,6 +199,75 @@
     demo.race,
     demo.ethnicity,
     exp.carcinogen_exposure
+LIMIT 100;</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT
+std.study_accession as "Study Accession",  
+    fil.data_file_name AS "File Name",
+    fil.data_file_format AS "Format",
+    fil.data_file_type AS "File Type",
+CASE     
+    WHEN fil.data_file_size &gt;= 1024 * 1024 * 1024 THEN 
+        CASE 
+            WHEN ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 2) = CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) 
+            THEN CAST(CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' GB'
+            ELSE ROUND(fil.data_file_size / (1024.0 * 1024.0 * 1024.0), 2) || ' GB'
+        END
+    WHEN fil.data_file_size &gt;= 1024 * 1024 THEN 
+        CASE 
+            WHEN ROUND(fil.data_file_size / (1024.0 * 1024.0), 2) = CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0), 0) AS INT) 
+            THEN CAST(CAST(ROUND(fil.data_file_size / (1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' MB'
+            ELSE ROUND(fil.data_file_size / (1024.0 * 1024.0), 2) || ' MB'
+        END
+    WHEN fil.data_file_size &gt;= 1024 THEN 
+        CASE 
+            WHEN ROUND(fil.data_file_size / 1024.0, 2) = CAST(ROUND(fil.data_file_size / 1024.0, 0) AS INT) 
+            THEN CAST(CAST(ROUND(fil.data_file_size / 1024.0, 0) AS INT) AS TEXT) || ' KB'
+            ELSE ROUND(fil.data_file_size / 1024.0, 2) || ' KB'
+        END
+    ELSE 
+        CASE 
+            WHEN ROUND(fil.data_file_size, 2) = CAST(ROUND(fil.data_file_size, 0) AS INT) 
+            THEN CAST(CAST(ROUND(fil.data_file_size, 0) AS INT) AS TEXT) || ' Bytes'
+            ELSE ROUND(fil.data_file_size, 2) || ' Bytes'
+        END
+    END AS "Size",
+    fil.data_file_description AS "Description",
+    fil."specimen.specimen_record_id" AS "Specimen Record ID",
+    prt.participant_id AS "Participant ID",
+    dgn.ctep_disease_term AS "Diagnosis"
+FROM 
+    df_study std
+LEFT JOIN 
+    df_participant prt 
+        ON std.study_short_name = prt."study.study_short_name"
+LEFT JOIN 
+    df_diagnosis dgn 
+        ON prt.participant_id = dgn."participant.participant_id"
+LEFT JOIN 
+    df_demographic demo 
+        ON prt.participant_id = demo."participant.participant_id"
+LEFT JOIN 
+    df_exposure exp 
+        ON prt.participant_id = exp."participant.participant_id"
+LEFT JOIN 
+    df_targeted_therapy tgt 
+        ON prt.participant_id = tgt."participant.participant_id"
+LEFT JOIN 
+    df_non_targeted_therapy ntt 
+        ON prt.participant_id = ntt."participant.participant_id"
+LEFT JOIN 
+    df_participant_status pst 
+        ON prt.participant_id = pst."participant.participant_id"
+LEFT JOIN 
+    df_biospecimen bio 
+        ON prt.participant_id = bio."participant.participant_id"
+LEFT JOIN 
+    df_file fil 
+        ON bio.specimen_record_id = fil."specimen.specimen_record_id"
+WHERE 
+    std.study_id = 'NCT04314401' AND bio.anatomical_collection_site = 'Neck' AND fil.data_file_name IS NOT NULL
 LIMIT 100;</t>
   </si>
 </sst>
@@ -688,16 +689,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="75.77734375" customWidth="1"/>
-    <col min="3" max="3" width="60.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -714,24 +715,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="297" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="297" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="372" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="372" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -739,16 +740,16 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
+      <c r="B4" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C5" s="1"/>
     </row>
   </sheetData>
